--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_monster_ai.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_monster_ai.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_monster_ai" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_monster_ai!$A$4:$AE$825</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_monster_ai!$A$4:$AE$828</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2774,12 +2774,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2802,6 +2796,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2980,12 +2980,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3059,6 +3053,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3331,19 +3331,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3352,7 +3352,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3376,16 +3376,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3394,28 +3394,28 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3514,10 +3514,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3535,34 +3533,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3574,10 +3572,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4564,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -4632,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -4836,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -4904,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -5167,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -5235,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -5693,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K23" s="5">
         <v>0</v>
@@ -5758,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K24" s="5">
         <v>0</v>
@@ -5823,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K25" s="5">
         <v>0</v>
@@ -5888,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K26" s="5">
         <v>0</v>
@@ -6278,7 +6276,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -6343,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -6408,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="1">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -6476,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -6544,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -6612,7 +6610,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -6680,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
@@ -6748,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -6816,7 +6814,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -6884,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -6952,7 +6950,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -7017,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -7082,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -7147,7 +7145,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -7212,7 +7210,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
@@ -7277,7 +7275,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
@@ -7342,7 +7340,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
@@ -7407,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
@@ -7472,7 +7470,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
@@ -7537,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
@@ -7602,7 +7600,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
@@ -7667,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
@@ -7732,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K54" s="5">
         <v>0</v>
@@ -7797,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K55" s="5">
         <v>0</v>
@@ -7862,7 +7860,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K56" s="5">
         <v>0</v>
@@ -7927,7 +7925,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K57" s="5">
         <v>0</v>
@@ -7992,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="I58" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K58" s="5">
         <v>0</v>
@@ -8057,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K59" s="5">
         <v>0</v>
@@ -8122,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K60" s="5">
         <v>0</v>
@@ -8187,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="I61" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K61" s="5">
         <v>0</v>
@@ -8252,7 +8250,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K62" s="5">
         <v>0</v>
@@ -8317,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K63" s="5">
         <v>0</v>
@@ -8382,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K64" s="5">
         <v>0</v>
@@ -8447,7 +8445,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K65" s="5">
         <v>0</v>
@@ -8512,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -8577,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -8642,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -8707,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
@@ -8772,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
@@ -8837,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K71" s="5">
         <v>0</v>
@@ -8902,7 +8900,7 @@
         <v>1</v>
       </c>
       <c r="I72" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
@@ -8967,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K73" s="5">
         <v>0</v>
@@ -9032,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="I74" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
@@ -9097,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
@@ -9162,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="I76" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K76" s="5">
         <v>0</v>
@@ -9227,7 +9225,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K77" s="5">
         <v>0</v>
@@ -9292,7 +9290,7 @@
         <v>1</v>
       </c>
       <c r="I78" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K78" s="5">
         <v>0</v>
@@ -9357,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="I79" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K79" s="5">
         <v>0</v>
@@ -9422,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="I80" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K80" s="5">
         <v>0</v>
@@ -9487,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="I81" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K81" s="5">
         <v>0</v>
@@ -9552,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K82" s="5">
         <v>0</v>
@@ -9617,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K83" s="5">
         <v>0</v>
@@ -9682,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K84" s="5">
         <v>0</v>
@@ -9747,7 +9745,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K85" s="5">
         <v>0</v>
@@ -9812,7 +9810,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K86" s="5">
         <v>0</v>
@@ -9877,7 +9875,7 @@
         <v>1</v>
       </c>
       <c r="I87" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K87" s="5">
         <v>0</v>
@@ -9942,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K88" s="5">
         <v>0</v>
@@ -10007,7 +10005,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K89" s="5">
         <v>0</v>
@@ -10072,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K90" s="5">
         <v>0</v>
@@ -10137,7 +10135,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K91" s="5">
         <v>0</v>
@@ -10202,7 +10200,7 @@
         <v>1</v>
       </c>
       <c r="I92" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K92" s="5">
         <v>0</v>
@@ -10267,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="I93" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K93" s="5">
         <v>0</v>
@@ -10332,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K94" s="5">
         <v>0</v>
@@ -10397,7 +10395,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K95" s="5">
         <v>0</v>
@@ -10462,7 +10460,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K96" s="5">
         <v>0</v>
@@ -10527,7 +10525,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K97" s="5">
         <v>0</v>
@@ -10592,7 +10590,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K98" s="5">
         <v>0</v>
@@ -10657,7 +10655,7 @@
         <v>1</v>
       </c>
       <c r="I99" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K99" s="5">
         <v>0</v>
@@ -10722,7 +10720,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K100" s="5">
         <v>0</v>
@@ -10787,7 +10785,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K101" s="5">
         <v>0</v>
@@ -10852,7 +10850,7 @@
         <v>1</v>
       </c>
       <c r="I102" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K102" s="5">
         <v>0</v>
@@ -10917,7 +10915,7 @@
         <v>1</v>
       </c>
       <c r="I103" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K103" s="5">
         <v>0</v>
@@ -10982,7 +10980,7 @@
         <v>1</v>
       </c>
       <c r="I104" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K104" s="5">
         <v>0</v>
@@ -11047,7 +11045,7 @@
         <v>1</v>
       </c>
       <c r="I105" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K105" s="5">
         <v>0</v>
@@ -11112,7 +11110,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
@@ -11177,7 +11175,7 @@
         <v>1</v>
       </c>
       <c r="I107" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K107" s="5">
         <v>0</v>
@@ -11242,7 +11240,7 @@
         <v>1</v>
       </c>
       <c r="I108" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K108" s="5">
         <v>0</v>
@@ -11307,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="I109" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
@@ -11372,7 +11370,7 @@
         <v>1</v>
       </c>
       <c r="I110" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K110" s="5">
         <v>0</v>
@@ -11437,7 +11435,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K111" s="5">
         <v>0</v>
@@ -11502,7 +11500,7 @@
         <v>1</v>
       </c>
       <c r="I112" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
@@ -11567,7 +11565,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
@@ -11632,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="I114" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K114" s="5">
         <v>0</v>
@@ -11697,7 +11695,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="5">
@@ -11767,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="I116" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J116" s="5"/>
       <c r="K116" s="5">
@@ -11837,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="I117" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="5">
@@ -11907,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="I118" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="5">
@@ -11977,7 +11975,7 @@
         <v>1</v>
       </c>
       <c r="I119" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="5">
@@ -12047,7 +12045,7 @@
         <v>1</v>
       </c>
       <c r="I120" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J120" s="5"/>
       <c r="K120" s="5">
@@ -12117,7 +12115,7 @@
         <v>1</v>
       </c>
       <c r="I121" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J121" s="5"/>
       <c r="K121" s="5">
@@ -12187,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="I122" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="5">
@@ -12257,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="I123" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="5">
@@ -12327,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="I124" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="5">
@@ -12397,7 +12395,7 @@
         <v>1</v>
       </c>
       <c r="I125" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J125" s="5"/>
       <c r="K125" s="5">
@@ -12467,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="I126" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J126" s="5"/>
       <c r="K126" s="5">
@@ -12537,7 +12535,7 @@
         <v>1</v>
       </c>
       <c r="I127" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="5">
@@ -12607,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="I128" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5">
@@ -12677,7 +12675,7 @@
         <v>1</v>
       </c>
       <c r="I129" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J129" s="5"/>
       <c r="K129" s="5">
@@ -12747,7 +12745,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J130" s="5"/>
       <c r="K130" s="5">
@@ -12817,7 +12815,7 @@
         <v>1</v>
       </c>
       <c r="I131" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J131" s="5"/>
       <c r="K131" s="5">
@@ -12887,7 +12885,7 @@
         <v>1</v>
       </c>
       <c r="I132" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="5">
@@ -12957,7 +12955,7 @@
         <v>1</v>
       </c>
       <c r="I133" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J133" s="5"/>
       <c r="K133" s="5">
@@ -13027,7 +13025,7 @@
         <v>1</v>
       </c>
       <c r="I134" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="5">
@@ -13097,7 +13095,7 @@
         <v>1</v>
       </c>
       <c r="I135" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5">
@@ -13167,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="I136" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J136" s="5"/>
       <c r="K136" s="5">
@@ -13237,7 +13235,7 @@
         <v>1</v>
       </c>
       <c r="I137" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J137" s="5"/>
       <c r="K137" s="5">
@@ -13307,7 +13305,7 @@
         <v>1</v>
       </c>
       <c r="I138" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="5">
@@ -13377,7 +13375,7 @@
         <v>1</v>
       </c>
       <c r="I139" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J139" s="5"/>
       <c r="K139" s="5">
@@ -13447,7 +13445,7 @@
         <v>1</v>
       </c>
       <c r="I140" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J140" s="5"/>
       <c r="K140" s="5">
@@ -13517,7 +13515,7 @@
         <v>1</v>
       </c>
       <c r="I141" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="5">
@@ -13587,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="I142" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J142" s="5"/>
       <c r="K142" s="5">
@@ -13657,7 +13655,7 @@
         <v>1</v>
       </c>
       <c r="I143" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J143" s="5"/>
       <c r="K143" s="5">
@@ -13727,7 +13725,7 @@
         <v>1</v>
       </c>
       <c r="I144" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J144" s="5"/>
       <c r="K144" s="5">
@@ -13869,7 +13867,7 @@
         <v>1</v>
       </c>
       <c r="I146" s="13">
-        <v>10800000</v>
+        <v>7200000</v>
       </c>
       <c r="J146" s="14"/>
       <c r="K146" s="2">
@@ -13941,7 +13939,7 @@
         <v>1</v>
       </c>
       <c r="I147" s="13">
-        <v>14400000</v>
+        <v>10800000</v>
       </c>
       <c r="J147" s="14"/>
       <c r="K147" s="2">
@@ -14013,7 +14011,7 @@
         <v>1</v>
       </c>
       <c r="I148" s="13">
-        <v>21600000</v>
+        <v>10800000</v>
       </c>
       <c r="J148" s="14"/>
       <c r="K148" s="2">
@@ -14084,7 +14082,7 @@
       <c r="H149" s="2">
         <v>1</v>
       </c>
-      <c r="I149" s="2">
+      <c r="I149" s="13">
         <v>0</v>
       </c>
       <c r="J149" s="14"/>
@@ -14154,7 +14152,7 @@
         <v>1</v>
       </c>
       <c r="I150" s="13">
-        <v>28800000</v>
+        <v>10800000</v>
       </c>
       <c r="J150" s="14"/>
       <c r="K150" s="2">
@@ -14223,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="I151" s="13">
-        <v>28800000</v>
+        <v>10800000</v>
       </c>
       <c r="J151" s="14"/>
       <c r="K151" s="2">
@@ -14568,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="I156" s="13">
-        <v>28800000</v>
+        <v>14400000</v>
       </c>
       <c r="J156" s="14"/>
       <c r="K156" s="2">
@@ -14775,7 +14773,7 @@
         <v>1</v>
       </c>
       <c r="I159" s="13">
-        <v>32400000</v>
+        <v>14400000</v>
       </c>
       <c r="J159" s="14"/>
       <c r="K159" s="2">
@@ -14982,7 +14980,7 @@
         <v>1</v>
       </c>
       <c r="I162" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J162" s="14"/>
       <c r="K162" s="2">
@@ -15051,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="I163" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J163" s="14"/>
       <c r="K163" s="2">
@@ -15189,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="I165" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J165" s="14"/>
       <c r="K165" s="5">
@@ -15258,7 +15256,7 @@
         <v>1</v>
       </c>
       <c r="I166" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J166" s="14"/>
       <c r="K166" s="5">
@@ -15327,7 +15325,7 @@
         <v>1</v>
       </c>
       <c r="I167" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J167" s="14"/>
       <c r="K167" s="5">
@@ -15396,7 +15394,7 @@
         <v>1</v>
       </c>
       <c r="I168" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J168" s="14"/>
       <c r="K168" s="5">
@@ -15465,7 +15463,7 @@
         <v>1</v>
       </c>
       <c r="I169" s="1">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J169" s="14"/>
       <c r="K169" s="5">
@@ -15534,7 +15532,7 @@
         <v>1</v>
       </c>
       <c r="I170" s="13">
-        <v>43200000</v>
+        <v>21600000</v>
       </c>
       <c r="J170" s="14"/>
       <c r="K170" s="5">
@@ -15603,7 +15601,7 @@
         <v>1</v>
       </c>
       <c r="I171" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J171" s="19"/>
       <c r="K171" s="5">
@@ -15672,7 +15670,7 @@
         <v>1</v>
       </c>
       <c r="I172" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J172" s="19"/>
       <c r="K172" s="5">
@@ -15741,7 +15739,7 @@
         <v>1</v>
       </c>
       <c r="I173" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="J173" s="19"/>
       <c r="K173" s="5">
@@ -15810,7 +15808,7 @@
         <v>1</v>
       </c>
       <c r="I174" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K174" s="5">
         <v>0</v>
@@ -15875,7 +15873,7 @@
         <v>1</v>
       </c>
       <c r="I175" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K175" s="5">
         <v>0</v>
@@ -15940,7 +15938,7 @@
         <v>1</v>
       </c>
       <c r="I176" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K176" s="5">
         <v>0</v>
@@ -16005,7 +16003,7 @@
         <v>1</v>
       </c>
       <c r="I177" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K177" s="5">
         <v>0</v>
@@ -16070,7 +16068,7 @@
         <v>1</v>
       </c>
       <c r="I178" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K178" s="5">
         <v>0</v>
@@ -16135,7 +16133,7 @@
         <v>1</v>
       </c>
       <c r="I179" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K179" s="5">
         <v>0</v>
@@ -16200,7 +16198,7 @@
         <v>1</v>
       </c>
       <c r="I180" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K180" s="5">
         <v>0</v>
@@ -16265,7 +16263,7 @@
         <v>1</v>
       </c>
       <c r="I181" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K181" s="5">
         <v>0</v>
@@ -16330,7 +16328,7 @@
         <v>1</v>
       </c>
       <c r="I182" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K182" s="5">
         <v>0</v>
@@ -16395,7 +16393,7 @@
         <v>1</v>
       </c>
       <c r="I183" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K183" s="5">
         <v>0</v>
@@ -16460,7 +16458,7 @@
         <v>1</v>
       </c>
       <c r="I184" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K184" s="5">
         <v>0</v>
@@ -16525,7 +16523,7 @@
         <v>1</v>
       </c>
       <c r="I185" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K185" s="5">
         <v>0</v>
@@ -16590,7 +16588,7 @@
         <v>1</v>
       </c>
       <c r="I186" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K186" s="5">
         <v>0</v>
@@ -16655,7 +16653,7 @@
         <v>1</v>
       </c>
       <c r="I187" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K187" s="5">
         <v>0</v>
@@ -16720,7 +16718,7 @@
         <v>1</v>
       </c>
       <c r="I188" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K188" s="5">
         <v>0</v>
@@ -16785,7 +16783,7 @@
         <v>1</v>
       </c>
       <c r="I189" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K189" s="5">
         <v>0</v>
@@ -16850,7 +16848,7 @@
         <v>1</v>
       </c>
       <c r="I190" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K190" s="5">
         <v>0</v>
@@ -16915,7 +16913,7 @@
         <v>1</v>
       </c>
       <c r="I191" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K191" s="5">
         <v>0</v>
@@ -16980,7 +16978,7 @@
         <v>1</v>
       </c>
       <c r="I192" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K192" s="5">
         <v>0</v>
@@ -17045,7 +17043,7 @@
         <v>1</v>
       </c>
       <c r="I193" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K193" s="5">
         <v>0</v>
@@ -17110,7 +17108,7 @@
         <v>1</v>
       </c>
       <c r="I194" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K194" s="5">
         <v>0</v>
@@ -17175,7 +17173,7 @@
         <v>1</v>
       </c>
       <c r="I195" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K195" s="5">
         <v>0</v>
@@ -17240,7 +17238,7 @@
         <v>1</v>
       </c>
       <c r="I196" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K196" s="5">
         <v>0</v>
@@ -17305,7 +17303,7 @@
         <v>1</v>
       </c>
       <c r="I197" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K197" s="5">
         <v>0</v>
@@ -17370,7 +17368,7 @@
         <v>1</v>
       </c>
       <c r="I198" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K198" s="5">
         <v>0</v>
@@ -17435,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="I199" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K199" s="5">
         <v>0</v>
@@ -17500,7 +17498,7 @@
         <v>1</v>
       </c>
       <c r="I200" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K200" s="5">
         <v>0</v>
@@ -17565,7 +17563,7 @@
         <v>1</v>
       </c>
       <c r="I201" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K201" s="5">
         <v>0</v>
@@ -17630,7 +17628,7 @@
         <v>1</v>
       </c>
       <c r="I202" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K202" s="5">
         <v>0</v>
@@ -17695,7 +17693,7 @@
         <v>1</v>
       </c>
       <c r="I203" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K203" s="5">
         <v>0</v>
@@ -17760,7 +17758,7 @@
         <v>1</v>
       </c>
       <c r="I204" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K204" s="5">
         <v>0</v>
@@ -17825,7 +17823,7 @@
         <v>1</v>
       </c>
       <c r="I205" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K205" s="5">
         <v>0</v>
@@ -17890,7 +17888,7 @@
         <v>1</v>
       </c>
       <c r="I206" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K206" s="5">
         <v>0</v>
@@ -17955,7 +17953,7 @@
         <v>1</v>
       </c>
       <c r="I207" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K207" s="5">
         <v>0</v>
@@ -18020,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="I208" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K208" s="5">
         <v>0</v>
@@ -18085,7 +18083,7 @@
         <v>1</v>
       </c>
       <c r="I209" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K209" s="5">
         <v>0</v>
@@ -18150,7 +18148,7 @@
         <v>1</v>
       </c>
       <c r="I210" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K210" s="5">
         <v>0</v>
@@ -18215,7 +18213,7 @@
         <v>1</v>
       </c>
       <c r="I211" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K211" s="5">
         <v>0</v>
@@ -18280,7 +18278,7 @@
         <v>1</v>
       </c>
       <c r="I212" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K212" s="5">
         <v>0</v>
@@ -18345,7 +18343,7 @@
         <v>1</v>
       </c>
       <c r="I213" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K213" s="5">
         <v>0</v>
@@ -18410,7 +18408,7 @@
         <v>1</v>
       </c>
       <c r="I214" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K214" s="5">
         <v>0</v>
@@ -18475,7 +18473,7 @@
         <v>1</v>
       </c>
       <c r="I215" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K215" s="5">
         <v>0</v>
@@ -23332,9 +23330,7 @@
       <c r="H292" s="5">
         <v>1</v>
       </c>
-      <c r="I292" s="5">
-        <v>30000</v>
-      </c>
+      <c r="I292" s="5"/>
       <c r="K292" s="5">
         <v>0</v>
       </c>
@@ -23400,9 +23396,7 @@
       <c r="H293" s="5">
         <v>1</v>
       </c>
-      <c r="I293" s="5">
-        <v>300000</v>
-      </c>
+      <c r="I293" s="5"/>
       <c r="K293" s="5">
         <v>0</v>
       </c>
@@ -23468,9 +23462,7 @@
       <c r="H294" s="5">
         <v>1</v>
       </c>
-      <c r="I294" s="5">
-        <v>300000</v>
-      </c>
+      <c r="I294" s="5"/>
       <c r="K294" s="5">
         <v>0</v>
       </c>
@@ -23536,9 +23528,7 @@
       <c r="H295" s="5">
         <v>1</v>
       </c>
-      <c r="I295" s="5">
-        <v>300000</v>
-      </c>
+      <c r="I295" s="5"/>
       <c r="K295" s="5">
         <v>0</v>
       </c>
@@ -23604,9 +23594,7 @@
       <c r="H296" s="5">
         <v>1</v>
       </c>
-      <c r="I296" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I296" s="5"/>
       <c r="K296" s="5">
         <v>0</v>
       </c>
@@ -23669,9 +23657,7 @@
       <c r="H297" s="5">
         <v>1</v>
       </c>
-      <c r="I297" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I297" s="5"/>
       <c r="K297" s="5">
         <v>0</v>
       </c>
@@ -23734,9 +23720,7 @@
       <c r="H298" s="5">
         <v>1</v>
       </c>
-      <c r="I298" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I298" s="5"/>
       <c r="K298" s="5">
         <v>0</v>
       </c>
@@ -23799,9 +23783,7 @@
       <c r="H299" s="5">
         <v>1</v>
       </c>
-      <c r="I299" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I299" s="5"/>
       <c r="K299" s="5">
         <v>0</v>
       </c>
@@ -23864,9 +23846,7 @@
       <c r="H300" s="5">
         <v>1</v>
       </c>
-      <c r="I300" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I300" s="5"/>
       <c r="K300" s="5">
         <v>0</v>
       </c>
@@ -23929,9 +23909,7 @@
       <c r="H301" s="5">
         <v>1</v>
       </c>
-      <c r="I301" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I301" s="5"/>
       <c r="K301" s="5">
         <v>0</v>
       </c>
@@ -23994,9 +23972,7 @@
       <c r="H302" s="5">
         <v>1</v>
       </c>
-      <c r="I302" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I302" s="5"/>
       <c r="K302" s="5">
         <v>0</v>
       </c>
@@ -24059,9 +24035,7 @@
       <c r="H303" s="5">
         <v>1</v>
       </c>
-      <c r="I303" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I303" s="5"/>
       <c r="K303" s="5">
         <v>0</v>
       </c>
@@ -24124,9 +24098,7 @@
       <c r="H304" s="5">
         <v>1</v>
       </c>
-      <c r="I304" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I304" s="5"/>
       <c r="K304" s="5">
         <v>0</v>
       </c>
@@ -24189,9 +24161,7 @@
       <c r="H305" s="5">
         <v>1</v>
       </c>
-      <c r="I305" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I305" s="5"/>
       <c r="K305" s="5">
         <v>0</v>
       </c>
@@ -24254,9 +24224,7 @@
       <c r="H306" s="5">
         <v>1</v>
       </c>
-      <c r="I306" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I306" s="5"/>
       <c r="K306" s="5">
         <v>0</v>
       </c>
@@ -24319,9 +24287,7 @@
       <c r="H307" s="5">
         <v>1</v>
       </c>
-      <c r="I307" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I307" s="5"/>
       <c r="K307" s="5">
         <v>0</v>
       </c>
@@ -24384,9 +24350,7 @@
       <c r="H308" s="5">
         <v>1</v>
       </c>
-      <c r="I308" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I308" s="5"/>
       <c r="K308" s="5">
         <v>0</v>
       </c>
@@ -24449,9 +24413,7 @@
       <c r="H309" s="5">
         <v>1</v>
       </c>
-      <c r="I309" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I309" s="5"/>
       <c r="K309" s="5">
         <v>0</v>
       </c>
@@ -24514,9 +24476,7 @@
       <c r="H310" s="5">
         <v>1</v>
       </c>
-      <c r="I310" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I310" s="5"/>
       <c r="K310" s="5">
         <v>0</v>
       </c>
@@ -24579,9 +24539,7 @@
       <c r="H311" s="5">
         <v>1</v>
       </c>
-      <c r="I311" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I311" s="5"/>
       <c r="K311" s="5">
         <v>0</v>
       </c>
@@ -24644,9 +24602,7 @@
       <c r="H312" s="5">
         <v>1</v>
       </c>
-      <c r="I312" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I312" s="5"/>
       <c r="K312" s="5">
         <v>0</v>
       </c>
@@ -24709,9 +24665,7 @@
       <c r="H313" s="5">
         <v>1</v>
       </c>
-      <c r="I313" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I313" s="5"/>
       <c r="K313" s="5">
         <v>0</v>
       </c>
@@ -24774,9 +24728,7 @@
       <c r="H314" s="5">
         <v>1</v>
       </c>
-      <c r="I314" s="5">
-        <v>900000</v>
-      </c>
+      <c r="I314" s="5"/>
       <c r="K314" s="5">
         <v>0</v>
       </c>
@@ -24839,9 +24791,7 @@
       <c r="H315" s="5">
         <v>1</v>
       </c>
-      <c r="I315" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I315" s="5"/>
       <c r="K315" s="5">
         <v>0</v>
       </c>
@@ -24904,9 +24854,7 @@
       <c r="H316" s="5">
         <v>1</v>
       </c>
-      <c r="I316" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I316" s="5"/>
       <c r="K316" s="5">
         <v>0</v>
       </c>
@@ -24969,9 +24917,7 @@
       <c r="H317" s="5">
         <v>1</v>
       </c>
-      <c r="I317" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I317" s="5"/>
       <c r="K317" s="5">
         <v>0</v>
       </c>
@@ -25034,9 +24980,7 @@
       <c r="H318" s="5">
         <v>1</v>
       </c>
-      <c r="I318" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I318" s="5"/>
       <c r="K318" s="5">
         <v>0</v>
       </c>
@@ -25099,9 +25043,7 @@
       <c r="H319" s="5">
         <v>1</v>
       </c>
-      <c r="I319" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I319" s="5"/>
       <c r="K319" s="5">
         <v>0</v>
       </c>
@@ -25164,9 +25106,7 @@
       <c r="H320" s="5">
         <v>1</v>
       </c>
-      <c r="I320" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I320" s="5"/>
       <c r="K320" s="5">
         <v>0</v>
       </c>
@@ -25229,9 +25169,7 @@
       <c r="H321" s="5">
         <v>1</v>
       </c>
-      <c r="I321" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I321" s="5"/>
       <c r="K321" s="5">
         <v>0</v>
       </c>
@@ -25294,9 +25232,7 @@
       <c r="H322" s="5">
         <v>1</v>
       </c>
-      <c r="I322" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I322" s="5"/>
       <c r="K322" s="5">
         <v>0</v>
       </c>
@@ -25359,9 +25295,7 @@
       <c r="H323" s="5">
         <v>1</v>
       </c>
-      <c r="I323" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I323" s="5"/>
       <c r="K323" s="5">
         <v>0</v>
       </c>
@@ -25424,9 +25358,7 @@
       <c r="H324" s="5">
         <v>1</v>
       </c>
-      <c r="I324" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I324" s="5"/>
       <c r="K324" s="5">
         <v>0</v>
       </c>
@@ -25489,9 +25421,7 @@
       <c r="H325" s="5">
         <v>1</v>
       </c>
-      <c r="I325" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I325" s="5"/>
       <c r="K325" s="5">
         <v>0</v>
       </c>
@@ -25554,9 +25484,7 @@
       <c r="H326" s="5">
         <v>1</v>
       </c>
-      <c r="I326" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I326" s="5"/>
       <c r="K326" s="5">
         <v>0</v>
       </c>
@@ -25619,9 +25547,7 @@
       <c r="H327" s="5">
         <v>1</v>
       </c>
-      <c r="I327" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I327" s="5"/>
       <c r="K327" s="5">
         <v>0</v>
       </c>
@@ -25684,9 +25610,7 @@
       <c r="H328" s="5">
         <v>1</v>
       </c>
-      <c r="I328" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I328" s="5"/>
       <c r="K328" s="5">
         <v>0</v>
       </c>
@@ -25749,9 +25673,7 @@
       <c r="H329" s="5">
         <v>1</v>
       </c>
-      <c r="I329" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I329" s="5"/>
       <c r="K329" s="5">
         <v>0</v>
       </c>
@@ -25814,9 +25736,7 @@
       <c r="H330" s="5">
         <v>1</v>
       </c>
-      <c r="I330" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I330" s="5"/>
       <c r="K330" s="5">
         <v>0</v>
       </c>
@@ -25879,9 +25799,7 @@
       <c r="H331" s="5">
         <v>1</v>
       </c>
-      <c r="I331" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I331" s="5"/>
       <c r="K331" s="5">
         <v>0</v>
       </c>
@@ -25944,9 +25862,7 @@
       <c r="H332" s="5">
         <v>1</v>
       </c>
-      <c r="I332" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I332" s="5"/>
       <c r="K332" s="5">
         <v>0</v>
       </c>
@@ -26009,9 +25925,7 @@
       <c r="H333" s="5">
         <v>1</v>
       </c>
-      <c r="I333" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I333" s="5"/>
       <c r="K333" s="5">
         <v>0</v>
       </c>
@@ -26074,9 +25988,7 @@
       <c r="H334" s="5">
         <v>1</v>
       </c>
-      <c r="I334" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I334" s="5"/>
       <c r="K334" s="5">
         <v>0</v>
       </c>
@@ -26139,9 +26051,7 @@
       <c r="H335" s="5">
         <v>1</v>
       </c>
-      <c r="I335" s="5">
-        <v>2400000</v>
-      </c>
+      <c r="I335" s="5"/>
       <c r="K335" s="5">
         <v>0</v>
       </c>
@@ -26205,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="I336" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K336" s="5">
         <v>0</v>
@@ -26270,7 +26180,7 @@
         <v>1</v>
       </c>
       <c r="I337" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K337" s="5">
         <v>0</v>
@@ -26335,7 +26245,7 @@
         <v>1</v>
       </c>
       <c r="I338" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K338" s="5">
         <v>0</v>
@@ -26400,7 +26310,7 @@
         <v>1</v>
       </c>
       <c r="I339" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K339" s="5">
         <v>0</v>
@@ -26465,7 +26375,7 @@
         <v>1</v>
       </c>
       <c r="I340" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K340" s="5">
         <v>0</v>
@@ -26530,7 +26440,7 @@
         <v>1</v>
       </c>
       <c r="I341" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K341" s="5">
         <v>0</v>
@@ -26595,7 +26505,7 @@
         <v>1</v>
       </c>
       <c r="I342" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K342" s="5">
         <v>0</v>
@@ -26660,7 +26570,7 @@
         <v>1</v>
       </c>
       <c r="I343" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K343" s="5">
         <v>0</v>
@@ -26725,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="I344" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K344" s="5">
         <v>0</v>
@@ -26790,7 +26700,7 @@
         <v>1</v>
       </c>
       <c r="I345" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K345" s="5">
         <v>0</v>
@@ -26855,7 +26765,7 @@
         <v>1</v>
       </c>
       <c r="I346" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K346" s="5">
         <v>0</v>
@@ -26920,7 +26830,7 @@
         <v>1</v>
       </c>
       <c r="I347" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K347" s="5">
         <v>0</v>
@@ -26985,7 +26895,7 @@
         <v>1</v>
       </c>
       <c r="I348" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K348" s="5">
         <v>0</v>
@@ -27050,7 +26960,7 @@
         <v>1</v>
       </c>
       <c r="I349" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K349" s="5">
         <v>0</v>
@@ -27115,7 +27025,7 @@
         <v>1</v>
       </c>
       <c r="I350" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K350" s="5">
         <v>0</v>
@@ -27180,7 +27090,7 @@
         <v>1</v>
       </c>
       <c r="I351" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K351" s="5">
         <v>0</v>
@@ -27245,7 +27155,7 @@
         <v>1</v>
       </c>
       <c r="I352" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K352" s="5">
         <v>0</v>
@@ -27310,7 +27220,7 @@
         <v>1</v>
       </c>
       <c r="I353" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K353" s="5">
         <v>0</v>
@@ -27375,7 +27285,7 @@
         <v>1</v>
       </c>
       <c r="I354" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K354" s="5">
         <v>0</v>
@@ -27440,7 +27350,7 @@
         <v>1</v>
       </c>
       <c r="I355" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K355" s="5">
         <v>0</v>
@@ -27505,7 +27415,7 @@
         <v>1</v>
       </c>
       <c r="I356" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K356" s="5">
         <v>0</v>
@@ -27570,7 +27480,7 @@
         <v>1</v>
       </c>
       <c r="I357" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K357" s="5">
         <v>0</v>
@@ -27635,7 +27545,7 @@
         <v>1</v>
       </c>
       <c r="I358" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K358" s="5">
         <v>0</v>
@@ -27700,7 +27610,7 @@
         <v>1</v>
       </c>
       <c r="I359" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K359" s="5">
         <v>0</v>
@@ -27765,7 +27675,7 @@
         <v>1</v>
       </c>
       <c r="I360" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K360" s="5">
         <v>0</v>
@@ -27830,7 +27740,7 @@
         <v>1</v>
       </c>
       <c r="I361" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K361" s="5">
         <v>0</v>
@@ -27895,7 +27805,7 @@
         <v>1</v>
       </c>
       <c r="I362" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K362" s="5">
         <v>0</v>
@@ -27960,7 +27870,7 @@
         <v>1</v>
       </c>
       <c r="I363" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K363" s="5">
         <v>0</v>
@@ -28025,7 +27935,7 @@
         <v>1</v>
       </c>
       <c r="I364" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K364" s="5">
         <v>0</v>
@@ -28090,7 +28000,7 @@
         <v>1</v>
       </c>
       <c r="I365" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K365" s="5">
         <v>0</v>
@@ -28155,7 +28065,7 @@
         <v>1</v>
       </c>
       <c r="I366" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K366" s="5">
         <v>0</v>
@@ -28220,7 +28130,7 @@
         <v>1</v>
       </c>
       <c r="I367" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K367" s="5">
         <v>0</v>
@@ -28285,7 +28195,7 @@
         <v>1</v>
       </c>
       <c r="I368" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K368" s="5">
         <v>0</v>
@@ -28350,7 +28260,7 @@
         <v>1</v>
       </c>
       <c r="I369" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K369" s="5">
         <v>0</v>
@@ -28415,7 +28325,7 @@
         <v>1</v>
       </c>
       <c r="I370" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K370" s="5">
         <v>0</v>
@@ -28480,7 +28390,7 @@
         <v>1</v>
       </c>
       <c r="I371" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K371" s="5">
         <v>0</v>
@@ -28545,7 +28455,7 @@
         <v>1</v>
       </c>
       <c r="I372" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K372" s="5">
         <v>0</v>
@@ -28610,7 +28520,7 @@
         <v>1</v>
       </c>
       <c r="I373" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K373" s="5">
         <v>0</v>
@@ -28675,7 +28585,7 @@
         <v>1</v>
       </c>
       <c r="I374" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K374" s="5">
         <v>0</v>
@@ -28740,7 +28650,7 @@
         <v>1</v>
       </c>
       <c r="I375" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K375" s="5">
         <v>0</v>
@@ -28805,7 +28715,7 @@
         <v>1</v>
       </c>
       <c r="I376" s="5">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K376" s="5">
         <v>0</v>
@@ -44932,9 +44842,7 @@
       <c r="H626" s="5">
         <v>1</v>
       </c>
-      <c r="I626" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I626" s="5"/>
       <c r="K626" s="5">
         <v>0</v>
       </c>
@@ -44997,9 +44905,7 @@
       <c r="H627" s="5">
         <v>1</v>
       </c>
-      <c r="I627" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I627" s="5"/>
       <c r="K627" s="5">
         <v>0</v>
       </c>
@@ -45063,9 +44969,7 @@
       <c r="H628" s="2">
         <v>1</v>
       </c>
-      <c r="I628" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I628" s="5"/>
       <c r="J628" s="14"/>
       <c r="K628" s="2">
         <v>0</v>
@@ -45137,9 +45041,7 @@
       <c r="H629" s="2">
         <v>1</v>
       </c>
-      <c r="I629" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I629" s="5"/>
       <c r="J629" s="14"/>
       <c r="K629" s="2">
         <v>0</v>
@@ -45210,9 +45112,7 @@
       <c r="H630" s="2">
         <v>1</v>
       </c>
-      <c r="I630" s="5">
-        <v>600000</v>
-      </c>
+      <c r="I630" s="5"/>
       <c r="J630" s="14"/>
       <c r="K630" s="2">
         <v>0</v>
@@ -47148,7 +47048,7 @@
         <v>1</v>
       </c>
       <c r="I660" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J660" s="30"/>
       <c r="K660" s="30">
@@ -47217,7 +47117,7 @@
         <v>1</v>
       </c>
       <c r="I661" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J661" s="30"/>
       <c r="K661" s="30">
@@ -47286,7 +47186,7 @@
         <v>1</v>
       </c>
       <c r="I662" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J662" s="30"/>
       <c r="K662" s="30">
@@ -47355,7 +47255,7 @@
         <v>1</v>
       </c>
       <c r="I663" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J663" s="30"/>
       <c r="K663" s="30">
@@ -47424,7 +47324,7 @@
         <v>1</v>
       </c>
       <c r="I664" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J664" s="30"/>
       <c r="K664" s="30">
@@ -47493,7 +47393,7 @@
         <v>1</v>
       </c>
       <c r="I665" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J665" s="30"/>
       <c r="K665" s="30">
@@ -47672,7 +47572,7 @@
         <v>1</v>
       </c>
       <c r="I668" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J668" s="30"/>
       <c r="K668" s="30">
@@ -47741,7 +47641,7 @@
         <v>1</v>
       </c>
       <c r="I669" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J669" s="30"/>
       <c r="K669" s="30">
@@ -47810,7 +47710,7 @@
         <v>1</v>
       </c>
       <c r="I670" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J670" s="30"/>
       <c r="K670" s="30">
@@ -47879,7 +47779,7 @@
         <v>1</v>
       </c>
       <c r="I671" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J671" s="30"/>
       <c r="K671" s="30">
@@ -47948,7 +47848,7 @@
         <v>1</v>
       </c>
       <c r="I672" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J672" s="30"/>
       <c r="K672" s="30">
@@ -48017,7 +47917,7 @@
         <v>1</v>
       </c>
       <c r="I673" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J673" s="30"/>
       <c r="K673" s="30">
@@ -48196,7 +48096,7 @@
         <v>1</v>
       </c>
       <c r="I676" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J676" s="30"/>
       <c r="K676" s="30">
@@ -48265,7 +48165,7 @@
         <v>1</v>
       </c>
       <c r="I677" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J677" s="30"/>
       <c r="K677" s="30">
@@ -48334,7 +48234,7 @@
         <v>1</v>
       </c>
       <c r="I678" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J678" s="30"/>
       <c r="K678" s="30">
@@ -48403,7 +48303,7 @@
         <v>1</v>
       </c>
       <c r="I679" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J679" s="30"/>
       <c r="K679" s="30">
@@ -48472,7 +48372,7 @@
         <v>1</v>
       </c>
       <c r="I680" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J680" s="30"/>
       <c r="K680" s="30">
@@ -48541,7 +48441,7 @@
         <v>1</v>
       </c>
       <c r="I681" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J681" s="30"/>
       <c r="K681" s="30">
@@ -48720,7 +48620,7 @@
         <v>1</v>
       </c>
       <c r="I684" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J684" s="30"/>
       <c r="K684" s="30">
@@ -48789,7 +48689,7 @@
         <v>1</v>
       </c>
       <c r="I685" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J685" s="30"/>
       <c r="K685" s="30">
@@ -48858,7 +48758,7 @@
         <v>1</v>
       </c>
       <c r="I686" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J686" s="30"/>
       <c r="K686" s="30">
@@ -48927,7 +48827,7 @@
         <v>1</v>
       </c>
       <c r="I687" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J687" s="30"/>
       <c r="K687" s="30">
@@ -48996,7 +48896,7 @@
         <v>1</v>
       </c>
       <c r="I688" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J688" s="30"/>
       <c r="K688" s="30">
@@ -49065,7 +48965,7 @@
         <v>1</v>
       </c>
       <c r="I689" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J689" s="30"/>
       <c r="K689" s="30">
@@ -49244,7 +49144,7 @@
         <v>1</v>
       </c>
       <c r="I692" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J692" s="30"/>
       <c r="K692" s="30">
@@ -49313,7 +49213,7 @@
         <v>1</v>
       </c>
       <c r="I693" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J693" s="30"/>
       <c r="K693" s="30">
@@ -49382,7 +49282,7 @@
         <v>1</v>
       </c>
       <c r="I694" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J694" s="30"/>
       <c r="K694" s="30">
@@ -49451,7 +49351,7 @@
         <v>1</v>
       </c>
       <c r="I695" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J695" s="30"/>
       <c r="K695" s="30">
@@ -49520,7 +49420,7 @@
         <v>1</v>
       </c>
       <c r="I696" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J696" s="30"/>
       <c r="K696" s="30">
@@ -49589,7 +49489,7 @@
         <v>1</v>
       </c>
       <c r="I697" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J697" s="30"/>
       <c r="K697" s="30">
@@ -49768,7 +49668,7 @@
         <v>1</v>
       </c>
       <c r="I700" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J700" s="30"/>
       <c r="K700" s="30">
@@ -49837,7 +49737,7 @@
         <v>1</v>
       </c>
       <c r="I701" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J701" s="30"/>
       <c r="K701" s="30">
@@ -49906,7 +49806,7 @@
         <v>1</v>
       </c>
       <c r="I702" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J702" s="30"/>
       <c r="K702" s="30">
@@ -49975,7 +49875,7 @@
         <v>1</v>
       </c>
       <c r="I703" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J703" s="30"/>
       <c r="K703" s="30">
@@ -50044,7 +49944,7 @@
         <v>1</v>
       </c>
       <c r="I704" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J704" s="30"/>
       <c r="K704" s="30">
@@ -50113,7 +50013,7 @@
         <v>1</v>
       </c>
       <c r="I705" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="J705" s="30"/>
       <c r="K705" s="30">
@@ -50292,7 +50192,7 @@
         <v>1</v>
       </c>
       <c r="I708" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="K708" s="30">
         <v>0</v>
@@ -50359,7 +50259,7 @@
         <v>1</v>
       </c>
       <c r="I709" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="K709" s="30">
         <v>0</v>
@@ -50426,7 +50326,7 @@
         <v>1</v>
       </c>
       <c r="I710" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="K710" s="30">
         <v>0</v>
@@ -50493,7 +50393,7 @@
         <v>1</v>
       </c>
       <c r="I711" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="K711" s="30">
         <v>0</v>
@@ -50560,7 +50460,7 @@
         <v>1</v>
       </c>
       <c r="I712" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="K712" s="30">
         <v>0</v>
@@ -50627,7 +50527,7 @@
         <v>1</v>
       </c>
       <c r="I713" s="30">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="K713" s="30">
         <v>0</v>
@@ -50800,7 +50700,7 @@
         <v>1</v>
       </c>
       <c r="I716" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K716" s="30">
         <v>0</v>
@@ -50867,7 +50767,7 @@
         <v>1</v>
       </c>
       <c r="I717" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K717" s="30">
         <v>0</v>
@@ -50934,7 +50834,7 @@
         <v>1</v>
       </c>
       <c r="I718" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K718" s="30">
         <v>0</v>
@@ -51001,7 +50901,7 @@
         <v>1</v>
       </c>
       <c r="I719" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K719" s="30">
         <v>0</v>
@@ -51068,7 +50968,7 @@
         <v>1</v>
       </c>
       <c r="I720" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K720" s="30">
         <v>0</v>
@@ -51135,7 +51035,7 @@
         <v>1</v>
       </c>
       <c r="I721" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K721" s="30">
         <v>0</v>
@@ -51202,7 +51102,7 @@
         <v>1</v>
       </c>
       <c r="I722" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K722" s="30">
         <v>0</v>
@@ -51269,7 +51169,7 @@
         <v>1</v>
       </c>
       <c r="I723" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K723" s="30">
         <v>0</v>
@@ -51336,7 +51236,7 @@
         <v>1</v>
       </c>
       <c r="I724" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K724" s="30">
         <v>0</v>
@@ -51403,7 +51303,7 @@
         <v>1</v>
       </c>
       <c r="I725" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K725" s="30">
         <v>0</v>
@@ -51470,7 +51370,7 @@
         <v>1</v>
       </c>
       <c r="I726" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K726" s="30">
         <v>0</v>
@@ -51537,7 +51437,7 @@
         <v>1</v>
       </c>
       <c r="I727" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K727" s="30">
         <v>0</v>
@@ -51604,7 +51504,7 @@
         <v>1</v>
       </c>
       <c r="I728" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K728" s="30">
         <v>0</v>
@@ -51671,7 +51571,7 @@
         <v>1</v>
       </c>
       <c r="I729" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K729" s="30">
         <v>0</v>
@@ -51738,7 +51638,7 @@
         <v>1</v>
       </c>
       <c r="I730" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K730" s="30">
         <v>0</v>
@@ -51805,7 +51705,7 @@
         <v>1</v>
       </c>
       <c r="I731" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K731" s="30">
         <v>0</v>
@@ -51872,7 +51772,7 @@
         <v>1</v>
       </c>
       <c r="I732" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K732" s="30">
         <v>0</v>
@@ -51939,7 +51839,7 @@
         <v>1</v>
       </c>
       <c r="I733" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K733" s="30">
         <v>0</v>
@@ -52006,7 +51906,7 @@
         <v>1</v>
       </c>
       <c r="I734" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K734" s="30">
         <v>0</v>
@@ -52073,7 +51973,7 @@
         <v>1</v>
       </c>
       <c r="I735" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K735" s="30">
         <v>0</v>
@@ -52140,7 +52040,7 @@
         <v>1</v>
       </c>
       <c r="I736" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K736" s="30">
         <v>0</v>
@@ -52207,7 +52107,7 @@
         <v>1</v>
       </c>
       <c r="I737" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K737" s="30">
         <v>0</v>
@@ -52274,7 +52174,7 @@
         <v>1</v>
       </c>
       <c r="I738" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K738" s="30">
         <v>0</v>
@@ -52341,7 +52241,7 @@
         <v>1</v>
       </c>
       <c r="I739" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K739" s="30">
         <v>0</v>
@@ -52408,7 +52308,7 @@
         <v>1</v>
       </c>
       <c r="I740" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K740" s="30">
         <v>0</v>
@@ -52475,7 +52375,7 @@
         <v>1</v>
       </c>
       <c r="I741" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K741" s="30">
         <v>0</v>
@@ -52542,7 +52442,7 @@
         <v>1</v>
       </c>
       <c r="I742" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K742" s="30">
         <v>0</v>
@@ -52609,7 +52509,7 @@
         <v>1</v>
       </c>
       <c r="I743" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K743" s="30">
         <v>0</v>
@@ -52676,7 +52576,7 @@
         <v>1</v>
       </c>
       <c r="I744" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K744" s="30">
         <v>0</v>
@@ -52743,7 +52643,7 @@
         <v>1</v>
       </c>
       <c r="I745" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K745" s="30">
         <v>0</v>
@@ -52810,7 +52710,7 @@
         <v>1</v>
       </c>
       <c r="I746" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K746" s="30">
         <v>0</v>
@@ -52877,7 +52777,7 @@
         <v>1</v>
       </c>
       <c r="I747" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K747" s="30">
         <v>0</v>
@@ -52944,7 +52844,7 @@
         <v>1</v>
       </c>
       <c r="I748" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K748" s="30">
         <v>0</v>
@@ -53011,7 +52911,7 @@
         <v>1</v>
       </c>
       <c r="I749" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K749" s="30">
         <v>0</v>
@@ -53078,7 +52978,7 @@
         <v>1</v>
       </c>
       <c r="I750" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K750" s="30">
         <v>0</v>
@@ -53145,7 +53045,7 @@
         <v>1</v>
       </c>
       <c r="I751" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K751" s="30">
         <v>0</v>
@@ -53212,7 +53112,7 @@
         <v>1</v>
       </c>
       <c r="I752" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K752" s="30">
         <v>0</v>
@@ -53279,7 +53179,7 @@
         <v>1</v>
       </c>
       <c r="I753" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K753" s="30">
         <v>0</v>
@@ -53346,7 +53246,7 @@
         <v>1</v>
       </c>
       <c r="I754" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K754" s="30">
         <v>0</v>
@@ -53413,7 +53313,7 @@
         <v>1</v>
       </c>
       <c r="I755" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K755" s="30">
         <v>0</v>
@@ -53480,7 +53380,7 @@
         <v>1</v>
       </c>
       <c r="I756" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K756" s="30">
         <v>0</v>
@@ -53547,7 +53447,7 @@
         <v>1</v>
       </c>
       <c r="I757" s="30">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="K757" s="30">
         <v>0</v>
@@ -53613,6 +53513,9 @@
       <c r="H758" s="5">
         <v>0</v>
       </c>
+      <c r="I758" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K758" s="5">
         <v>0</v>
       </c>
@@ -53675,6 +53578,9 @@
       <c r="H759" s="5">
         <v>0</v>
       </c>
+      <c r="I759" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K759" s="5">
         <v>0</v>
       </c>
@@ -53737,6 +53643,9 @@
       <c r="H760" s="5">
         <v>0</v>
       </c>
+      <c r="I760" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K760" s="5">
         <v>0</v>
       </c>
@@ -53799,6 +53708,9 @@
       <c r="H761" s="5">
         <v>0</v>
       </c>
+      <c r="I761" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K761" s="5">
         <v>0</v>
       </c>
@@ -53861,6 +53773,9 @@
       <c r="H762" s="5">
         <v>0</v>
       </c>
+      <c r="I762" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K762" s="5">
         <v>0</v>
       </c>
@@ -53923,6 +53838,9 @@
       <c r="H763" s="5">
         <v>0</v>
       </c>
+      <c r="I763" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K763" s="5">
         <v>0</v>
       </c>
@@ -53985,6 +53903,9 @@
       <c r="H764" s="5">
         <v>0</v>
       </c>
+      <c r="I764" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K764" s="5">
         <v>0</v>
       </c>
@@ -54047,6 +53968,9 @@
       <c r="H765" s="5">
         <v>0</v>
       </c>
+      <c r="I765" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K765" s="5">
         <v>0</v>
       </c>
@@ -54109,6 +54033,9 @@
       <c r="H766" s="5">
         <v>0</v>
       </c>
+      <c r="I766" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K766" s="5">
         <v>0</v>
       </c>
@@ -54171,6 +54098,9 @@
       <c r="H767" s="5">
         <v>0</v>
       </c>
+      <c r="I767" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K767" s="5">
         <v>0</v>
       </c>
@@ -54233,6 +54163,9 @@
       <c r="H768" s="5">
         <v>0</v>
       </c>
+      <c r="I768" s="13">
+        <v>86400000</v>
+      </c>
       <c r="K768" s="5">
         <v>0</v>
       </c>
@@ -58111,7 +58044,7 @@
       <c r="X828" s="30"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:AE825" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:AE828" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A30">

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_monster_ai.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_monster_ai.xlsx
@@ -5484,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F20" s="5">
         <v>12</v>
@@ -5549,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F21" s="5">
         <v>12</v>
@@ -5614,7 +5614,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F22" s="5">
         <v>12</v>
@@ -5679,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F23" s="5">
         <v>12</v>
@@ -5744,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F24" s="5">
         <v>12</v>
@@ -5809,7 +5809,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F25" s="5">
         <v>12</v>
@@ -5874,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F26" s="5">
         <v>12</v>
@@ -5939,7 +5939,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F27" s="5">
         <v>12</v>
@@ -6004,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F28" s="5">
         <v>12</v>
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F29" s="5">
         <v>12</v>
@@ -6134,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F30" s="5">
         <v>12</v>
@@ -6199,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F31" s="5">
         <v>12</v>
@@ -6264,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F32" s="5">
         <v>12</v>
@@ -6329,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F33" s="5">
         <v>12</v>
@@ -6394,7 +6394,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F34" s="5">
         <v>12</v>
@@ -6462,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5">
         <v>12</v>
@@ -6530,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F36" s="5">
         <v>12</v>
@@ -6598,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F37" s="5">
         <v>12</v>
@@ -6666,7 +6666,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F38" s="5">
         <v>12</v>
@@ -6734,7 +6734,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F39" s="5">
         <v>12</v>
@@ -6802,7 +6802,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F40" s="5">
         <v>12</v>
@@ -6870,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F41" s="5">
         <v>12</v>
@@ -6938,7 +6938,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F42" s="5">
         <v>12</v>
@@ -7003,7 +7003,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" s="5">
         <v>12</v>
@@ -7068,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F44" s="5">
         <v>12</v>
@@ -7133,7 +7133,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F45" s="5">
         <v>12</v>
@@ -7198,7 +7198,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F46" s="5">
         <v>12</v>
@@ -7263,7 +7263,7 @@
         <v>1</v>
       </c>
       <c r="E47" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F47" s="5">
         <v>12</v>
@@ -7328,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F48" s="5">
         <v>12</v>
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F49" s="5">
         <v>12</v>
@@ -7458,7 +7458,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F50" s="5">
         <v>12</v>
@@ -7523,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F51" s="5">
         <v>12</v>
@@ -7588,7 +7588,7 @@
         <v>2</v>
       </c>
       <c r="E52" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F52" s="5">
         <v>12</v>
@@ -7653,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F53" s="5">
         <v>12</v>
@@ -7718,7 +7718,7 @@
         <v>2</v>
       </c>
       <c r="E54" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F54" s="5">
         <v>12</v>
@@ -7783,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F55" s="5">
         <v>12</v>
@@ -7848,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" s="5">
         <v>12</v>
@@ -7913,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="E57" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F57" s="5">
         <v>12</v>
@@ -7978,7 +7978,7 @@
         <v>3</v>
       </c>
       <c r="E58" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F58" s="5">
         <v>12</v>
@@ -8043,7 +8043,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F59" s="5">
         <v>12</v>
@@ -8108,7 +8108,7 @@
         <v>5</v>
       </c>
       <c r="E60" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F60" s="5">
         <v>12</v>
@@ -8173,7 +8173,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F61" s="5">
         <v>12</v>
@@ -8238,7 +8238,7 @@
         <v>3</v>
       </c>
       <c r="E62" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F62" s="5">
         <v>12</v>
@@ -8303,7 +8303,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F63" s="5">
         <v>12</v>
@@ -8368,7 +8368,7 @@
         <v>3</v>
       </c>
       <c r="E64" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F64" s="5">
         <v>12</v>
@@ -8433,7 +8433,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F65" s="5">
         <v>12</v>
@@ -8498,7 +8498,7 @@
         <v>5</v>
       </c>
       <c r="E66" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F66" s="5">
         <v>12</v>
@@ -8563,7 +8563,7 @@
         <v>5</v>
       </c>
       <c r="E67" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F67" s="5">
         <v>12</v>
@@ -8628,7 +8628,7 @@
         <v>5</v>
       </c>
       <c r="E68" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F68" s="5">
         <v>12</v>
@@ -8693,7 +8693,7 @@
         <v>5</v>
       </c>
       <c r="E69" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F69" s="5">
         <v>12</v>
@@ -8758,7 +8758,7 @@
         <v>5</v>
       </c>
       <c r="E70" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F70" s="5">
         <v>12</v>
@@ -8823,7 +8823,7 @@
         <v>5</v>
       </c>
       <c r="E71" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F71" s="5">
         <v>12</v>
@@ -8888,7 +8888,7 @@
         <v>5</v>
       </c>
       <c r="E72" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F72" s="5">
         <v>12</v>
@@ -8953,7 +8953,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F73" s="5">
         <v>12</v>
@@ -9018,7 +9018,7 @@
         <v>5</v>
       </c>
       <c r="E74" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F74" s="5">
         <v>12</v>
@@ -9083,7 +9083,7 @@
         <v>5</v>
       </c>
       <c r="E75" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F75" s="5">
         <v>12</v>
@@ -9148,7 +9148,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F76" s="5">
         <v>12</v>
@@ -9213,7 +9213,7 @@
         <v>2</v>
       </c>
       <c r="E77" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F77" s="5">
         <v>12</v>
@@ -9278,7 +9278,7 @@
         <v>2</v>
       </c>
       <c r="E78" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F78" s="5">
         <v>12</v>
@@ -9343,7 +9343,7 @@
         <v>5</v>
       </c>
       <c r="E79" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F79" s="5">
         <v>12</v>
@@ -9408,7 +9408,7 @@
         <v>5</v>
       </c>
       <c r="E80" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F80" s="5">
         <v>12</v>
@@ -9473,7 +9473,7 @@
         <v>5</v>
       </c>
       <c r="E81" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F81" s="5">
         <v>12</v>
@@ -9538,7 +9538,7 @@
         <v>5</v>
       </c>
       <c r="E82" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F82" s="5">
         <v>12</v>
@@ -9603,7 +9603,7 @@
         <v>5</v>
       </c>
       <c r="E83" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F83" s="5">
         <v>12</v>
@@ -9668,7 +9668,7 @@
         <v>5</v>
       </c>
       <c r="E84" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F84" s="5">
         <v>12</v>
@@ -9733,7 +9733,7 @@
         <v>5</v>
       </c>
       <c r="E85" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F85" s="5">
         <v>12</v>
@@ -9798,7 +9798,7 @@
         <v>5</v>
       </c>
       <c r="E86" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F86" s="5">
         <v>12</v>
@@ -9863,7 +9863,7 @@
         <v>5</v>
       </c>
       <c r="E87" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F87" s="5">
         <v>12</v>
@@ -9928,7 +9928,7 @@
         <v>5</v>
       </c>
       <c r="E88" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F88" s="5">
         <v>12</v>
@@ -9993,7 +9993,7 @@
         <v>5</v>
       </c>
       <c r="E89" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F89" s="5">
         <v>12</v>
@@ -10058,7 +10058,7 @@
         <v>5</v>
       </c>
       <c r="E90" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F90" s="5">
         <v>12</v>
@@ -10123,7 +10123,7 @@
         <v>5</v>
       </c>
       <c r="E91" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F91" s="5">
         <v>12</v>
@@ -10188,7 +10188,7 @@
         <v>5</v>
       </c>
       <c r="E92" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F92" s="5">
         <v>12</v>
@@ -10253,7 +10253,7 @@
         <v>5</v>
       </c>
       <c r="E93" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F93" s="5">
         <v>12</v>
@@ -10318,7 +10318,7 @@
         <v>5</v>
       </c>
       <c r="E94" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F94" s="5">
         <v>12</v>
@@ -10383,7 +10383,7 @@
         <v>5</v>
       </c>
       <c r="E95" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F95" s="5">
         <v>12</v>
@@ -10448,7 +10448,7 @@
         <v>5</v>
       </c>
       <c r="E96" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F96" s="5">
         <v>12</v>
@@ -10513,7 +10513,7 @@
         <v>5</v>
       </c>
       <c r="E97" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F97" s="5">
         <v>12</v>
@@ -10578,7 +10578,7 @@
         <v>5</v>
       </c>
       <c r="E98" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F98" s="5">
         <v>12</v>
@@ -10643,7 +10643,7 @@
         <v>5</v>
       </c>
       <c r="E99" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F99" s="5">
         <v>12</v>
@@ -10708,7 +10708,7 @@
         <v>5</v>
       </c>
       <c r="E100" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F100" s="5">
         <v>12</v>
@@ -10773,7 +10773,7 @@
         <v>5</v>
       </c>
       <c r="E101" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F101" s="5">
         <v>12</v>
@@ -10838,7 +10838,7 @@
         <v>5</v>
       </c>
       <c r="E102" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F102" s="5">
         <v>12</v>
@@ -10903,7 +10903,7 @@
         <v>5</v>
       </c>
       <c r="E103" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F103" s="5">
         <v>12</v>
@@ -10968,7 +10968,7 @@
         <v>5</v>
       </c>
       <c r="E104" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F104" s="5">
         <v>12</v>
@@ -11033,7 +11033,7 @@
         <v>5</v>
       </c>
       <c r="E105" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F105" s="5">
         <v>12</v>
@@ -11098,7 +11098,7 @@
         <v>5</v>
       </c>
       <c r="E106" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F106" s="5">
         <v>12</v>
@@ -11163,7 +11163,7 @@
         <v>5</v>
       </c>
       <c r="E107" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F107" s="5">
         <v>12</v>
@@ -11228,7 +11228,7 @@
         <v>5</v>
       </c>
       <c r="E108" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F108" s="5">
         <v>12</v>
@@ -11293,7 +11293,7 @@
         <v>5</v>
       </c>
       <c r="E109" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F109" s="5">
         <v>12</v>
@@ -11358,7 +11358,7 @@
         <v>5</v>
       </c>
       <c r="E110" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F110" s="5">
         <v>12</v>
@@ -11423,7 +11423,7 @@
         <v>5</v>
       </c>
       <c r="E111" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F111" s="5">
         <v>12</v>
@@ -11488,7 +11488,7 @@
         <v>5</v>
       </c>
       <c r="E112" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F112" s="5">
         <v>12</v>
@@ -11553,7 +11553,7 @@
         <v>5</v>
       </c>
       <c r="E113" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F113" s="5">
         <v>12</v>
@@ -11618,7 +11618,7 @@
         <v>5</v>
       </c>
       <c r="E114" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F114" s="5">
         <v>12</v>
@@ -11683,7 +11683,7 @@
         <v>5</v>
       </c>
       <c r="E115" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F115" s="5">
         <v>12</v>
@@ -11753,7 +11753,7 @@
         <v>5</v>
       </c>
       <c r="E116" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F116" s="5">
         <v>12</v>
@@ -11823,7 +11823,7 @@
         <v>5</v>
       </c>
       <c r="E117" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F117" s="5">
         <v>12</v>
@@ -11893,7 +11893,7 @@
         <v>5</v>
       </c>
       <c r="E118" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F118" s="5">
         <v>12</v>
@@ -11963,7 +11963,7 @@
         <v>5</v>
       </c>
       <c r="E119" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F119" s="5">
         <v>12</v>
@@ -12033,7 +12033,7 @@
         <v>5</v>
       </c>
       <c r="E120" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F120" s="5">
         <v>12</v>
@@ -12103,7 +12103,7 @@
         <v>5</v>
       </c>
       <c r="E121" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F121" s="5">
         <v>12</v>
@@ -12173,7 +12173,7 @@
         <v>5</v>
       </c>
       <c r="E122" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F122" s="5">
         <v>12</v>
@@ -12243,7 +12243,7 @@
         <v>5</v>
       </c>
       <c r="E123" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F123" s="5">
         <v>12</v>
@@ -12313,7 +12313,7 @@
         <v>5</v>
       </c>
       <c r="E124" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F124" s="5">
         <v>12</v>
@@ -12383,7 +12383,7 @@
         <v>5</v>
       </c>
       <c r="E125" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F125" s="5">
         <v>12</v>
@@ -12453,7 +12453,7 @@
         <v>5</v>
       </c>
       <c r="E126" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F126" s="5">
         <v>12</v>
@@ -12523,7 +12523,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F127" s="5">
         <v>12</v>
@@ -12593,7 +12593,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F128" s="5">
         <v>12</v>
@@ -12663,7 +12663,7 @@
         <v>5</v>
       </c>
       <c r="E129" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F129" s="5">
         <v>12</v>
@@ -12943,7 +12943,7 @@
         <v>5</v>
       </c>
       <c r="E133" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F133" s="5">
         <v>12</v>
@@ -13013,7 +13013,7 @@
         <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F134" s="5">
         <v>12</v>
@@ -13083,7 +13083,7 @@
         <v>5</v>
       </c>
       <c r="E135" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F135" s="5">
         <v>12</v>
@@ -13153,7 +13153,7 @@
         <v>5</v>
       </c>
       <c r="E136" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F136" s="5">
         <v>12</v>
@@ -13223,7 +13223,7 @@
         <v>5</v>
       </c>
       <c r="E137" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F137" s="5">
         <v>12</v>
@@ -13293,7 +13293,7 @@
         <v>5</v>
       </c>
       <c r="E138" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F138" s="5">
         <v>12</v>
@@ -13363,7 +13363,7 @@
         <v>5</v>
       </c>
       <c r="E139" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F139" s="5">
         <v>12</v>
@@ -13433,7 +13433,7 @@
         <v>5</v>
       </c>
       <c r="E140" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F140" s="5">
         <v>12</v>
@@ -13503,7 +13503,7 @@
         <v>5</v>
       </c>
       <c r="E141" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F141" s="5">
         <v>12</v>
@@ -13573,7 +13573,7 @@
         <v>5</v>
       </c>
       <c r="E142" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F142" s="5">
         <v>12</v>
@@ -13643,7 +13643,7 @@
         <v>5</v>
       </c>
       <c r="E143" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F143" s="5">
         <v>12</v>
@@ -13713,7 +13713,7 @@
         <v>5</v>
       </c>
       <c r="E144" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F144" s="5">
         <v>12</v>
@@ -13783,7 +13783,7 @@
         <v>5</v>
       </c>
       <c r="E145" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F145" s="5">
         <v>12</v>
@@ -13855,7 +13855,7 @@
         <v>5</v>
       </c>
       <c r="E146" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F146" s="5">
         <v>12</v>
@@ -13927,7 +13927,7 @@
         <v>5</v>
       </c>
       <c r="E147" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F147" s="5">
         <v>12</v>
@@ -13999,7 +13999,7 @@
         <v>5</v>
       </c>
       <c r="E148" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F148" s="5">
         <v>12</v>
@@ -14071,7 +14071,7 @@
         <v>5</v>
       </c>
       <c r="E149" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F149" s="5">
         <v>12</v>
@@ -14140,7 +14140,7 @@
         <v>5</v>
       </c>
       <c r="E150" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F150" s="5">
         <v>12</v>
@@ -14209,7 +14209,7 @@
         <v>5</v>
       </c>
       <c r="E151" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F151" s="5">
         <v>12</v>
@@ -14278,7 +14278,7 @@
         <v>5</v>
       </c>
       <c r="E152" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F152" s="5">
         <v>12</v>
@@ -14347,7 +14347,7 @@
         <v>5</v>
       </c>
       <c r="E153" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F153" s="5">
         <v>12</v>
@@ -14416,7 +14416,7 @@
         <v>5</v>
       </c>
       <c r="E154" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F154" s="5">
         <v>12</v>
@@ -14485,7 +14485,7 @@
         <v>5</v>
       </c>
       <c r="E155" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F155" s="5">
         <v>12</v>
@@ -14554,7 +14554,7 @@
         <v>5</v>
       </c>
       <c r="E156" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F156" s="5">
         <v>12</v>
@@ -14623,7 +14623,7 @@
         <v>5</v>
       </c>
       <c r="E157" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F157" s="5">
         <v>12</v>
@@ -14692,7 +14692,7 @@
         <v>5</v>
       </c>
       <c r="E158" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F158" s="5">
         <v>12</v>
@@ -14761,7 +14761,7 @@
         <v>5</v>
       </c>
       <c r="E159" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F159" s="5">
         <v>12</v>
@@ -14830,7 +14830,7 @@
         <v>5</v>
       </c>
       <c r="E160" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F160" s="5">
         <v>12</v>
@@ -14899,7 +14899,7 @@
         <v>5</v>
       </c>
       <c r="E161" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F161" s="5">
         <v>12</v>
@@ -14968,7 +14968,7 @@
         <v>5</v>
       </c>
       <c r="E162" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F162" s="5">
         <v>12</v>
@@ -15037,7 +15037,7 @@
         <v>5</v>
       </c>
       <c r="E163" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F163" s="5">
         <v>12</v>
@@ -15106,7 +15106,7 @@
         <v>5</v>
       </c>
       <c r="E164" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F164" s="5">
         <v>12</v>
@@ -15175,7 +15175,7 @@
         <v>5</v>
       </c>
       <c r="E165" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F165" s="5">
         <v>12</v>
@@ -15244,7 +15244,7 @@
         <v>5</v>
       </c>
       <c r="E166" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F166" s="5">
         <v>12</v>
@@ -15313,7 +15313,7 @@
         <v>5</v>
       </c>
       <c r="E167" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F167" s="5">
         <v>12</v>
@@ -15382,7 +15382,7 @@
         <v>5</v>
       </c>
       <c r="E168" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F168" s="5">
         <v>12</v>
@@ -15451,7 +15451,7 @@
         <v>5</v>
       </c>
       <c r="E169" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F169" s="5">
         <v>12</v>
@@ -15520,7 +15520,7 @@
         <v>5</v>
       </c>
       <c r="E170" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F170" s="5">
         <v>12</v>
@@ -15589,7 +15589,7 @@
         <v>5</v>
       </c>
       <c r="E171" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F171" s="5">
         <v>12</v>
@@ -15658,7 +15658,7 @@
         <v>5</v>
       </c>
       <c r="E172" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F172" s="5">
         <v>12</v>
@@ -15727,7 +15727,7 @@
         <v>5</v>
       </c>
       <c r="E173" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F173" s="5">
         <v>12</v>
@@ -15796,7 +15796,7 @@
         <v>5</v>
       </c>
       <c r="E174" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F174" s="5">
         <v>12</v>
@@ -15861,7 +15861,7 @@
         <v>5</v>
       </c>
       <c r="E175" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F175" s="5">
         <v>12</v>
@@ -15926,7 +15926,7 @@
         <v>5</v>
       </c>
       <c r="E176" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F176" s="5">
         <v>12</v>
@@ -15991,7 +15991,7 @@
         <v>5</v>
       </c>
       <c r="E177" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F177" s="5">
         <v>12</v>
@@ -16056,7 +16056,7 @@
         <v>5</v>
       </c>
       <c r="E178" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F178" s="5">
         <v>12</v>
@@ -16121,7 +16121,7 @@
         <v>5</v>
       </c>
       <c r="E179" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F179" s="5">
         <v>12</v>
@@ -17356,7 +17356,7 @@
         <v>5</v>
       </c>
       <c r="E198" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F198" s="5">
         <v>12</v>
@@ -17421,7 +17421,7 @@
         <v>5</v>
       </c>
       <c r="E199" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F199" s="5">
         <v>12</v>
@@ -17486,7 +17486,7 @@
         <v>5</v>
       </c>
       <c r="E200" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F200" s="5">
         <v>12</v>
@@ -17551,7 +17551,7 @@
         <v>5</v>
       </c>
       <c r="E201" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F201" s="5">
         <v>12</v>
@@ -17616,7 +17616,7 @@
         <v>5</v>
       </c>
       <c r="E202" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F202" s="5">
         <v>12</v>
@@ -17681,7 +17681,7 @@
         <v>5</v>
       </c>
       <c r="E203" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F203" s="5">
         <v>12</v>
@@ -18588,7 +18588,7 @@
         <v>5</v>
       </c>
       <c r="E217" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F217" s="5">
         <v>12</v>
@@ -18654,7 +18654,7 @@
         <v>5</v>
       </c>
       <c r="E218" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F218" s="5">
         <v>12</v>
@@ -18720,7 +18720,7 @@
         <v>5</v>
       </c>
       <c r="E219" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F219" s="5">
         <v>12</v>
@@ -18783,7 +18783,7 @@
         <v>5</v>
       </c>
       <c r="E220" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F220" s="5">
         <v>12</v>
@@ -18846,7 +18846,7 @@
         <v>5</v>
       </c>
       <c r="E221" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F221" s="5">
         <v>12</v>
@@ -18909,7 +18909,7 @@
         <v>5</v>
       </c>
       <c r="E222" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F222" s="5">
         <v>12</v>
@@ -18972,7 +18972,7 @@
         <v>5</v>
       </c>
       <c r="E223" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F223" s="5">
         <v>12</v>
@@ -19035,7 +19035,7 @@
         <v>5</v>
       </c>
       <c r="E224" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F224" s="5">
         <v>12</v>
@@ -19098,7 +19098,7 @@
         <v>5</v>
       </c>
       <c r="E225" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F225" s="5">
         <v>12</v>
@@ -19161,7 +19161,7 @@
         <v>5</v>
       </c>
       <c r="E226" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F226" s="5">
         <v>12</v>
@@ -19224,7 +19224,7 @@
         <v>5</v>
       </c>
       <c r="E227" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F227" s="5">
         <v>12</v>
@@ -19287,7 +19287,7 @@
         <v>5</v>
       </c>
       <c r="E228" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F228" s="5">
         <v>12</v>
@@ -19350,7 +19350,7 @@
         <v>5</v>
       </c>
       <c r="E229" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F229" s="5">
         <v>12</v>
@@ -19413,7 +19413,7 @@
         <v>5</v>
       </c>
       <c r="E230" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F230" s="5">
         <v>12</v>
@@ -19476,7 +19476,7 @@
         <v>5</v>
       </c>
       <c r="E231" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F231" s="5">
         <v>12</v>
@@ -19539,7 +19539,7 @@
         <v>5</v>
       </c>
       <c r="E232" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F232" s="5">
         <v>12</v>
@@ -19602,7 +19602,7 @@
         <v>5</v>
       </c>
       <c r="E233" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F233" s="5">
         <v>12</v>
@@ -19665,7 +19665,7 @@
         <v>5</v>
       </c>
       <c r="E234" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F234" s="5">
         <v>12</v>
@@ -19728,7 +19728,7 @@
         <v>5</v>
       </c>
       <c r="E235" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F235" s="5">
         <v>12</v>
@@ -19791,7 +19791,7 @@
         <v>5</v>
       </c>
       <c r="E236" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F236" s="5">
         <v>12</v>
@@ -19854,7 +19854,7 @@
         <v>5</v>
       </c>
       <c r="E237" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F237" s="5">
         <v>12</v>
@@ -19917,7 +19917,7 @@
         <v>5</v>
       </c>
       <c r="E238" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F238" s="5">
         <v>12</v>
@@ -19980,7 +19980,7 @@
         <v>5</v>
       </c>
       <c r="E239" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F239" s="5">
         <v>12</v>
@@ -20043,7 +20043,7 @@
         <v>5</v>
       </c>
       <c r="E240" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F240" s="5">
         <v>12</v>
@@ -20106,7 +20106,7 @@
         <v>5</v>
       </c>
       <c r="E241" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F241" s="5">
         <v>12</v>
@@ -20169,7 +20169,7 @@
         <v>5</v>
       </c>
       <c r="E242" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F242" s="5">
         <v>12</v>
@@ -20232,7 +20232,7 @@
         <v>5</v>
       </c>
       <c r="E243" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F243" s="5">
         <v>12</v>
@@ -20295,7 +20295,7 @@
         <v>5</v>
       </c>
       <c r="E244" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F244" s="5">
         <v>12</v>
@@ -20358,7 +20358,7 @@
         <v>5</v>
       </c>
       <c r="E245" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F245" s="5">
         <v>12</v>
@@ -20421,7 +20421,7 @@
         <v>5</v>
       </c>
       <c r="E246" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F246" s="5">
         <v>12</v>
@@ -20484,7 +20484,7 @@
         <v>5</v>
       </c>
       <c r="E247" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F247" s="5">
         <v>12</v>
@@ -20547,7 +20547,7 @@
         <v>5</v>
       </c>
       <c r="E248" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F248" s="5">
         <v>12</v>
@@ -20610,7 +20610,7 @@
         <v>5</v>
       </c>
       <c r="E249" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F249" s="5">
         <v>12</v>
@@ -20673,7 +20673,7 @@
         <v>5</v>
       </c>
       <c r="E250" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F250" s="5">
         <v>12</v>
@@ -20736,7 +20736,7 @@
         <v>5</v>
       </c>
       <c r="E251" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F251" s="5">
         <v>12</v>
@@ -20799,7 +20799,7 @@
         <v>5</v>
       </c>
       <c r="E252" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F252" s="5">
         <v>12</v>
@@ -23330,7 +23330,6 @@
       <c r="H292" s="5">
         <v>1</v>
       </c>
-      <c r="I292" s="5"/>
       <c r="K292" s="5">
         <v>0</v>
       </c>
@@ -23396,7 +23395,6 @@
       <c r="H293" s="5">
         <v>1</v>
       </c>
-      <c r="I293" s="5"/>
       <c r="K293" s="5">
         <v>0</v>
       </c>
@@ -23462,7 +23460,6 @@
       <c r="H294" s="5">
         <v>1</v>
       </c>
-      <c r="I294" s="5"/>
       <c r="K294" s="5">
         <v>0</v>
       </c>
@@ -23528,7 +23525,6 @@
       <c r="H295" s="5">
         <v>1</v>
       </c>
-      <c r="I295" s="5"/>
       <c r="K295" s="5">
         <v>0</v>
       </c>
@@ -23594,7 +23590,6 @@
       <c r="H296" s="5">
         <v>1</v>
       </c>
-      <c r="I296" s="5"/>
       <c r="K296" s="5">
         <v>0</v>
       </c>
@@ -23657,7 +23652,6 @@
       <c r="H297" s="5">
         <v>1</v>
       </c>
-      <c r="I297" s="5"/>
       <c r="K297" s="5">
         <v>0</v>
       </c>
@@ -23720,7 +23714,6 @@
       <c r="H298" s="5">
         <v>1</v>
       </c>
-      <c r="I298" s="5"/>
       <c r="K298" s="5">
         <v>0</v>
       </c>
@@ -23783,7 +23776,6 @@
       <c r="H299" s="5">
         <v>1</v>
       </c>
-      <c r="I299" s="5"/>
       <c r="K299" s="5">
         <v>0</v>
       </c>
@@ -23846,7 +23838,6 @@
       <c r="H300" s="5">
         <v>1</v>
       </c>
-      <c r="I300" s="5"/>
       <c r="K300" s="5">
         <v>0</v>
       </c>
@@ -23909,7 +23900,6 @@
       <c r="H301" s="5">
         <v>1</v>
       </c>
-      <c r="I301" s="5"/>
       <c r="K301" s="5">
         <v>0</v>
       </c>
@@ -23972,7 +23962,6 @@
       <c r="H302" s="5">
         <v>1</v>
       </c>
-      <c r="I302" s="5"/>
       <c r="K302" s="5">
         <v>0</v>
       </c>
@@ -24035,7 +24024,6 @@
       <c r="H303" s="5">
         <v>1</v>
       </c>
-      <c r="I303" s="5"/>
       <c r="K303" s="5">
         <v>0</v>
       </c>
@@ -24098,7 +24086,6 @@
       <c r="H304" s="5">
         <v>1</v>
       </c>
-      <c r="I304" s="5"/>
       <c r="K304" s="5">
         <v>0</v>
       </c>
@@ -24161,7 +24148,6 @@
       <c r="H305" s="5">
         <v>1</v>
       </c>
-      <c r="I305" s="5"/>
       <c r="K305" s="5">
         <v>0</v>
       </c>
@@ -24224,7 +24210,6 @@
       <c r="H306" s="5">
         <v>1</v>
       </c>
-      <c r="I306" s="5"/>
       <c r="K306" s="5">
         <v>0</v>
       </c>
@@ -24287,7 +24272,6 @@
       <c r="H307" s="5">
         <v>1</v>
       </c>
-      <c r="I307" s="5"/>
       <c r="K307" s="5">
         <v>0</v>
       </c>
@@ -24350,7 +24334,6 @@
       <c r="H308" s="5">
         <v>1</v>
       </c>
-      <c r="I308" s="5"/>
       <c r="K308" s="5">
         <v>0</v>
       </c>
@@ -24413,7 +24396,6 @@
       <c r="H309" s="5">
         <v>1</v>
       </c>
-      <c r="I309" s="5"/>
       <c r="K309" s="5">
         <v>0</v>
       </c>
@@ -24476,7 +24458,6 @@
       <c r="H310" s="5">
         <v>1</v>
       </c>
-      <c r="I310" s="5"/>
       <c r="K310" s="5">
         <v>0</v>
       </c>
@@ -24539,7 +24520,6 @@
       <c r="H311" s="5">
         <v>1</v>
       </c>
-      <c r="I311" s="5"/>
       <c r="K311" s="5">
         <v>0</v>
       </c>
@@ -24602,7 +24582,6 @@
       <c r="H312" s="5">
         <v>1</v>
       </c>
-      <c r="I312" s="5"/>
       <c r="K312" s="5">
         <v>0</v>
       </c>
@@ -24665,7 +24644,6 @@
       <c r="H313" s="5">
         <v>1</v>
       </c>
-      <c r="I313" s="5"/>
       <c r="K313" s="5">
         <v>0</v>
       </c>
@@ -24728,7 +24706,6 @@
       <c r="H314" s="5">
         <v>1</v>
       </c>
-      <c r="I314" s="5"/>
       <c r="K314" s="5">
         <v>0</v>
       </c>
@@ -24791,7 +24768,6 @@
       <c r="H315" s="5">
         <v>1</v>
       </c>
-      <c r="I315" s="5"/>
       <c r="K315" s="5">
         <v>0</v>
       </c>
@@ -24854,7 +24830,6 @@
       <c r="H316" s="5">
         <v>1</v>
       </c>
-      <c r="I316" s="5"/>
       <c r="K316" s="5">
         <v>0</v>
       </c>
@@ -24917,7 +24892,6 @@
       <c r="H317" s="5">
         <v>1</v>
       </c>
-      <c r="I317" s="5"/>
       <c r="K317" s="5">
         <v>0</v>
       </c>
@@ -24980,7 +24954,6 @@
       <c r="H318" s="5">
         <v>1</v>
       </c>
-      <c r="I318" s="5"/>
       <c r="K318" s="5">
         <v>0</v>
       </c>
@@ -25043,7 +25016,6 @@
       <c r="H319" s="5">
         <v>1</v>
       </c>
-      <c r="I319" s="5"/>
       <c r="K319" s="5">
         <v>0</v>
       </c>
@@ -25106,7 +25078,6 @@
       <c r="H320" s="5">
         <v>1</v>
       </c>
-      <c r="I320" s="5"/>
       <c r="K320" s="5">
         <v>0</v>
       </c>
@@ -25169,7 +25140,6 @@
       <c r="H321" s="5">
         <v>1</v>
       </c>
-      <c r="I321" s="5"/>
       <c r="K321" s="5">
         <v>0</v>
       </c>
@@ -25232,7 +25202,6 @@
       <c r="H322" s="5">
         <v>1</v>
       </c>
-      <c r="I322" s="5"/>
       <c r="K322" s="5">
         <v>0</v>
       </c>
@@ -25295,7 +25264,6 @@
       <c r="H323" s="5">
         <v>1</v>
       </c>
-      <c r="I323" s="5"/>
       <c r="K323" s="5">
         <v>0</v>
       </c>
@@ -25358,7 +25326,6 @@
       <c r="H324" s="5">
         <v>1</v>
       </c>
-      <c r="I324" s="5"/>
       <c r="K324" s="5">
         <v>0</v>
       </c>
@@ -25421,7 +25388,6 @@
       <c r="H325" s="5">
         <v>1</v>
       </c>
-      <c r="I325" s="5"/>
       <c r="K325" s="5">
         <v>0</v>
       </c>
@@ -25484,7 +25450,6 @@
       <c r="H326" s="5">
         <v>1</v>
       </c>
-      <c r="I326" s="5"/>
       <c r="K326" s="5">
         <v>0</v>
       </c>
@@ -25547,7 +25512,6 @@
       <c r="H327" s="5">
         <v>1</v>
       </c>
-      <c r="I327" s="5"/>
       <c r="K327" s="5">
         <v>0</v>
       </c>
@@ -25610,7 +25574,6 @@
       <c r="H328" s="5">
         <v>1</v>
       </c>
-      <c r="I328" s="5"/>
       <c r="K328" s="5">
         <v>0</v>
       </c>
@@ -25673,7 +25636,6 @@
       <c r="H329" s="5">
         <v>1</v>
       </c>
-      <c r="I329" s="5"/>
       <c r="K329" s="5">
         <v>0</v>
       </c>
@@ -25736,7 +25698,6 @@
       <c r="H330" s="5">
         <v>1</v>
       </c>
-      <c r="I330" s="5"/>
       <c r="K330" s="5">
         <v>0</v>
       </c>
@@ -25799,7 +25760,6 @@
       <c r="H331" s="5">
         <v>1</v>
       </c>
-      <c r="I331" s="5"/>
       <c r="K331" s="5">
         <v>0</v>
       </c>
@@ -25862,7 +25822,6 @@
       <c r="H332" s="5">
         <v>1</v>
       </c>
-      <c r="I332" s="5"/>
       <c r="K332" s="5">
         <v>0</v>
       </c>
@@ -25925,7 +25884,6 @@
       <c r="H333" s="5">
         <v>1</v>
       </c>
-      <c r="I333" s="5"/>
       <c r="K333" s="5">
         <v>0</v>
       </c>
@@ -25988,7 +25946,6 @@
       <c r="H334" s="5">
         <v>1</v>
       </c>
-      <c r="I334" s="5"/>
       <c r="K334" s="5">
         <v>0</v>
       </c>
@@ -26051,7 +26008,6 @@
       <c r="H335" s="5">
         <v>1</v>
       </c>
-      <c r="I335" s="5"/>
       <c r="K335" s="5">
         <v>0</v>
       </c>
@@ -44842,7 +44798,6 @@
       <c r="H626" s="5">
         <v>1</v>
       </c>
-      <c r="I626" s="5"/>
       <c r="K626" s="5">
         <v>0</v>
       </c>
@@ -44905,7 +44860,6 @@
       <c r="H627" s="5">
         <v>1</v>
       </c>
-      <c r="I627" s="5"/>
       <c r="K627" s="5">
         <v>0</v>
       </c>
@@ -44969,7 +44923,6 @@
       <c r="H628" s="2">
         <v>1</v>
       </c>
-      <c r="I628" s="5"/>
       <c r="J628" s="14"/>
       <c r="K628" s="2">
         <v>0</v>
@@ -45041,7 +44994,6 @@
       <c r="H629" s="2">
         <v>1</v>
       </c>
-      <c r="I629" s="5"/>
       <c r="J629" s="14"/>
       <c r="K629" s="2">
         <v>0</v>
@@ -45112,7 +45064,6 @@
       <c r="H630" s="2">
         <v>1</v>
       </c>
-      <c r="I630" s="5"/>
       <c r="J630" s="14"/>
       <c r="K630" s="2">
         <v>0</v>
@@ -50688,10 +50639,10 @@
         <v>6</v>
       </c>
       <c r="E716" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F716" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G716" s="30">
         <v>5</v>
@@ -50755,10 +50706,10 @@
         <v>6</v>
       </c>
       <c r="E717" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F717" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G717" s="30">
         <v>5</v>
@@ -50822,10 +50773,10 @@
         <v>6</v>
       </c>
       <c r="E718" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F718" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G718" s="30">
         <v>5</v>
@@ -50889,10 +50840,10 @@
         <v>6</v>
       </c>
       <c r="E719" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F719" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G719" s="30">
         <v>5</v>
@@ -50956,10 +50907,10 @@
         <v>6</v>
       </c>
       <c r="E720" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F720" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G720" s="30">
         <v>5</v>
@@ -51023,10 +50974,10 @@
         <v>6</v>
       </c>
       <c r="E721" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F721" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G721" s="30">
         <v>5</v>
@@ -51090,10 +51041,10 @@
         <v>6</v>
       </c>
       <c r="E722" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F722" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G722" s="30">
         <v>5</v>
@@ -51157,10 +51108,10 @@
         <v>6</v>
       </c>
       <c r="E723" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F723" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G723" s="30">
         <v>5</v>
@@ -51224,10 +51175,10 @@
         <v>6</v>
       </c>
       <c r="E724" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F724" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G724" s="30">
         <v>5</v>
@@ -51291,10 +51242,10 @@
         <v>6</v>
       </c>
       <c r="E725" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F725" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G725" s="30">
         <v>5</v>
@@ -51358,10 +51309,10 @@
         <v>6</v>
       </c>
       <c r="E726" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F726" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G726" s="30">
         <v>5</v>
@@ -51425,10 +51376,10 @@
         <v>6</v>
       </c>
       <c r="E727" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F727" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G727" s="30">
         <v>5</v>
@@ -51492,10 +51443,10 @@
         <v>6</v>
       </c>
       <c r="E728" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F728" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G728" s="30">
         <v>5</v>
@@ -51559,10 +51510,10 @@
         <v>6</v>
       </c>
       <c r="E729" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F729" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G729" s="30">
         <v>5</v>
@@ -51626,10 +51577,10 @@
         <v>6</v>
       </c>
       <c r="E730" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F730" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G730" s="30">
         <v>5</v>
@@ -51693,10 +51644,10 @@
         <v>6</v>
       </c>
       <c r="E731" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F731" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G731" s="30">
         <v>5</v>
@@ -51760,10 +51711,10 @@
         <v>6</v>
       </c>
       <c r="E732" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F732" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G732" s="30">
         <v>5</v>
@@ -51827,10 +51778,10 @@
         <v>6</v>
       </c>
       <c r="E733" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F733" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G733" s="30">
         <v>5</v>
@@ -51894,10 +51845,10 @@
         <v>6</v>
       </c>
       <c r="E734" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F734" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G734" s="30">
         <v>5</v>
@@ -51961,10 +51912,10 @@
         <v>6</v>
       </c>
       <c r="E735" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F735" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G735" s="30">
         <v>5</v>
@@ -52028,10 +51979,10 @@
         <v>6</v>
       </c>
       <c r="E736" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F736" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G736" s="30">
         <v>5</v>
@@ -52095,10 +52046,10 @@
         <v>6</v>
       </c>
       <c r="E737" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F737" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G737" s="30">
         <v>5</v>
@@ -52162,10 +52113,10 @@
         <v>6</v>
       </c>
       <c r="E738" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F738" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G738" s="30">
         <v>5</v>
@@ -52229,10 +52180,10 @@
         <v>6</v>
       </c>
       <c r="E739" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F739" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G739" s="30">
         <v>5</v>
@@ -52296,10 +52247,10 @@
         <v>6</v>
       </c>
       <c r="E740" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F740" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G740" s="30">
         <v>5</v>
@@ -52363,10 +52314,10 @@
         <v>6</v>
       </c>
       <c r="E741" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F741" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G741" s="30">
         <v>5</v>
@@ -52430,10 +52381,10 @@
         <v>6</v>
       </c>
       <c r="E742" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F742" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G742" s="30">
         <v>5</v>
@@ -52497,10 +52448,10 @@
         <v>6</v>
       </c>
       <c r="E743" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F743" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G743" s="30">
         <v>5</v>
@@ -52564,10 +52515,10 @@
         <v>6</v>
       </c>
       <c r="E744" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F744" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G744" s="30">
         <v>5</v>
@@ -52631,10 +52582,10 @@
         <v>6</v>
       </c>
       <c r="E745" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F745" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G745" s="30">
         <v>5</v>
@@ -52698,10 +52649,10 @@
         <v>6</v>
       </c>
       <c r="E746" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F746" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G746" s="30">
         <v>5</v>
@@ -52765,10 +52716,10 @@
         <v>6</v>
       </c>
       <c r="E747" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F747" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G747" s="30">
         <v>5</v>
@@ -52832,10 +52783,10 @@
         <v>6</v>
       </c>
       <c r="E748" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F748" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G748" s="30">
         <v>5</v>
@@ -52899,10 +52850,10 @@
         <v>6</v>
       </c>
       <c r="E749" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F749" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G749" s="30">
         <v>5</v>
@@ -52966,10 +52917,10 @@
         <v>6</v>
       </c>
       <c r="E750" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F750" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G750" s="30">
         <v>5</v>
@@ -53033,10 +52984,10 @@
         <v>6</v>
       </c>
       <c r="E751" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F751" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G751" s="30">
         <v>5</v>
@@ -53100,10 +53051,10 @@
         <v>6</v>
       </c>
       <c r="E752" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F752" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G752" s="30">
         <v>5</v>
@@ -53167,10 +53118,10 @@
         <v>6</v>
       </c>
       <c r="E753" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F753" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G753" s="30">
         <v>5</v>
@@ -53234,10 +53185,10 @@
         <v>6</v>
       </c>
       <c r="E754" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F754" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G754" s="30">
         <v>5</v>
@@ -53301,10 +53252,10 @@
         <v>6</v>
       </c>
       <c r="E755" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F755" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G755" s="30">
         <v>5</v>
@@ -53368,10 +53319,10 @@
         <v>6</v>
       </c>
       <c r="E756" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F756" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G756" s="30">
         <v>5</v>
@@ -53435,10 +53386,10 @@
         <v>6</v>
       </c>
       <c r="E757" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F757" s="30">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G757" s="30">
         <v>5</v>
@@ -53501,8 +53452,8 @@
       <c r="D758" s="5">
         <v>5</v>
       </c>
-      <c r="E758" s="5">
-        <v>7</v>
+      <c r="E758" s="30">
+        <v>12</v>
       </c>
       <c r="F758" s="5">
         <v>12</v>
@@ -53566,8 +53517,8 @@
       <c r="D759" s="5">
         <v>5</v>
       </c>
-      <c r="E759" s="5">
-        <v>7</v>
+      <c r="E759" s="30">
+        <v>12</v>
       </c>
       <c r="F759" s="5">
         <v>12</v>
@@ -53631,8 +53582,8 @@
       <c r="D760" s="5">
         <v>5</v>
       </c>
-      <c r="E760" s="5">
-        <v>7</v>
+      <c r="E760" s="30">
+        <v>12</v>
       </c>
       <c r="F760" s="5">
         <v>12</v>
@@ -53696,8 +53647,8 @@
       <c r="D761" s="5">
         <v>5</v>
       </c>
-      <c r="E761" s="5">
-        <v>7</v>
+      <c r="E761" s="30">
+        <v>12</v>
       </c>
       <c r="F761" s="5">
         <v>12</v>
@@ -53761,8 +53712,8 @@
       <c r="D762" s="5">
         <v>5</v>
       </c>
-      <c r="E762" s="5">
-        <v>7</v>
+      <c r="E762" s="30">
+        <v>12</v>
       </c>
       <c r="F762" s="5">
         <v>12</v>
@@ -53826,8 +53777,8 @@
       <c r="D763" s="5">
         <v>5</v>
       </c>
-      <c r="E763" s="5">
-        <v>7</v>
+      <c r="E763" s="30">
+        <v>12</v>
       </c>
       <c r="F763" s="5">
         <v>7</v>
@@ -53891,8 +53842,8 @@
       <c r="D764" s="5">
         <v>5</v>
       </c>
-      <c r="E764" s="5">
-        <v>7</v>
+      <c r="E764" s="30">
+        <v>12</v>
       </c>
       <c r="F764" s="5">
         <v>12</v>
@@ -53956,8 +53907,8 @@
       <c r="D765" s="5">
         <v>5</v>
       </c>
-      <c r="E765" s="5">
-        <v>7</v>
+      <c r="E765" s="30">
+        <v>12</v>
       </c>
       <c r="F765" s="5">
         <v>7</v>
@@ -54021,8 +53972,8 @@
       <c r="D766" s="5">
         <v>5</v>
       </c>
-      <c r="E766" s="5">
-        <v>7</v>
+      <c r="E766" s="30">
+        <v>12</v>
       </c>
       <c r="F766" s="5">
         <v>12</v>
@@ -54086,8 +54037,8 @@
       <c r="D767" s="5">
         <v>5</v>
       </c>
-      <c r="E767" s="5">
-        <v>7</v>
+      <c r="E767" s="30">
+        <v>12</v>
       </c>
       <c r="F767" s="5">
         <v>7</v>
@@ -54151,8 +54102,8 @@
       <c r="D768" s="5">
         <v>5</v>
       </c>
-      <c r="E768" s="5">
-        <v>7</v>
+      <c r="E768" s="30">
+        <v>12</v>
       </c>
       <c r="F768" s="5">
         <v>7</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_monster_ai.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_monster_ai.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_monster_ai" sheetId="1" r:id="rId1"/>
